--- a/output/nabos_03_01avg.xlsx
+++ b/output/nabos_03_01avg.xlsx
@@ -544,7 +544,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2.969</v>
+        <v>2.948</v>
       </c>
       <c r="B2" t="n">
         <v>74.46143</v>
@@ -556,64 +556,64 @@
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.3168</v>
+        <v>-1.3145</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3072</v>
+        <v>-1.3013</v>
       </c>
       <c r="G2" t="n">
-        <v>22.200718</v>
+        <v>22.21243</v>
       </c>
       <c r="H2" t="n">
-        <v>22.256904</v>
+        <v>22.290682</v>
       </c>
       <c r="I2" t="n">
-        <v>27.2225</v>
+        <v>27.2364</v>
       </c>
       <c r="J2" t="n">
-        <v>27.289</v>
+        <v>27.3289</v>
       </c>
       <c r="K2" t="n">
-        <v>372.704</v>
+        <v>372.607</v>
       </c>
       <c r="L2" t="n">
-        <v>361.233</v>
+        <v>361.255</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1406</v>
+        <v>0.1628</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5918</v>
+        <v>4.5914</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1065</v>
+        <v>0.1067</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1065</v>
+        <v>0.1067</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0839</v>
+        <v>0.0842</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0306</v>
+        <v>0.0315</v>
       </c>
       <c r="S2" t="n">
-        <v>4376</v>
+        <v>4372</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0384</v>
+        <v>3.0356</v>
       </c>
       <c r="U2" t="n">
-        <v>55.36</v>
+        <v>55.34</v>
       </c>
       <c r="V2" t="n">
-        <v>2.5782</v>
+        <v>2.578</v>
       </c>
       <c r="W2" t="n">
-        <v>2.2283</v>
+        <v>2.2293</v>
       </c>
       <c r="X2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -636,7 +636,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3.958</v>
+        <v>3.961</v>
       </c>
       <c r="B3" t="n">
         <v>74.46145</v>
@@ -648,64 +648,64 @@
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.2911</v>
+        <v>-1.2939</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2882</v>
+        <v>-1.2901</v>
       </c>
       <c r="G3" t="n">
-        <v>22.355544</v>
+        <v>22.338979</v>
       </c>
       <c r="H3" t="n">
-        <v>22.370509</v>
+        <v>22.358796</v>
       </c>
       <c r="I3" t="n">
-        <v>27.406</v>
+        <v>27.3861</v>
       </c>
       <c r="J3" t="n">
-        <v>27.4234</v>
+        <v>27.4092</v>
       </c>
       <c r="K3" t="n">
-        <v>372.315</v>
+        <v>372.442</v>
       </c>
       <c r="L3" t="n">
-        <v>361.483</v>
+        <v>361.448</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1721</v>
+        <v>0.1726</v>
       </c>
       <c r="N3" t="n">
-        <v>4.5913</v>
+        <v>4.592</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1058</v>
+        <v>0.1055</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1058</v>
+        <v>0.1055</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0842</v>
+        <v>0.0836</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0318</v>
+        <v>0.0319</v>
       </c>
       <c r="S3" t="n">
-        <v>4539</v>
+        <v>4556</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1512</v>
+        <v>3.163</v>
       </c>
       <c r="U3" t="n">
-        <v>55.02</v>
+        <v>54.99</v>
       </c>
       <c r="V3" t="n">
-        <v>2.5804</v>
+        <v>2.5806</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2321</v>
+        <v>2.2317</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -728,76 +728,76 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4.948</v>
+        <v>4.947</v>
       </c>
       <c r="B4" t="n">
         <v>74.46148</v>
       </c>
       <c r="C4" t="n">
-        <v>169.90128</v>
+        <v>169.90129</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.3057</v>
+        <v>-1.3051</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2989</v>
+        <v>-1.2973</v>
       </c>
       <c r="G4" t="n">
-        <v>22.277056</v>
+        <v>22.282989</v>
       </c>
       <c r="H4" t="n">
-        <v>22.313072</v>
+        <v>22.320079</v>
       </c>
       <c r="I4" t="n">
-        <v>27.3135</v>
+        <v>27.3212</v>
       </c>
       <c r="J4" t="n">
-        <v>27.3556</v>
+        <v>27.3638</v>
       </c>
       <c r="K4" t="n">
-        <v>373.054</v>
+        <v>373.017</v>
       </c>
       <c r="L4" t="n">
-        <v>361.602</v>
+        <v>361.502</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1837</v>
+        <v>0.186</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5928</v>
+        <v>4.593</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1047</v>
+        <v>0.105</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1047</v>
+        <v>0.105</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0829</v>
+        <v>0.0828</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0323</v>
+        <v>0.0324</v>
       </c>
       <c r="S4" t="n">
-        <v>4804</v>
+        <v>4812</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3352</v>
+        <v>3.341</v>
       </c>
       <c r="U4" t="n">
         <v>53.8</v>
       </c>
       <c r="V4" t="n">
-        <v>2.5818</v>
+        <v>2.5817</v>
       </c>
       <c r="W4" t="n">
-        <v>2.231</v>
+        <v>2.2307</v>
       </c>
       <c r="X4" t="n">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -832,64 +832,64 @@
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2963</v>
+        <v>-1.2974</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2957</v>
+        <v>-1.2961</v>
       </c>
       <c r="G5" t="n">
-        <v>22.346268</v>
+        <v>22.338255</v>
       </c>
       <c r="H5" t="n">
-        <v>22.347984</v>
+        <v>22.3441</v>
       </c>
       <c r="I5" t="n">
-        <v>27.3972</v>
+        <v>27.3875</v>
       </c>
       <c r="J5" t="n">
-        <v>27.399</v>
+        <v>27.3942</v>
       </c>
       <c r="K5" t="n">
-        <v>372.376</v>
+        <v>372.41</v>
       </c>
       <c r="L5" t="n">
-        <v>361.599</v>
+        <v>361.652</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1726</v>
+        <v>0.1758</v>
       </c>
       <c r="N5" t="n">
         <v>4.5924</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1044</v>
+        <v>0.104</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1044</v>
+        <v>0.104</v>
       </c>
       <c r="Q5" t="n">
         <v>0.0833</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0319</v>
+        <v>0.032</v>
       </c>
       <c r="S5" t="n">
-        <v>4880</v>
+        <v>4885</v>
       </c>
       <c r="T5" t="n">
-        <v>3.3883</v>
+        <v>3.3916</v>
       </c>
       <c r="U5" t="n">
-        <v>50.74</v>
+        <v>48.69</v>
       </c>
       <c r="V5" t="n">
         <v>2.5797</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2315</v>
+        <v>2.2316</v>
       </c>
       <c r="X5" t="n">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -924,64 +924,64 @@
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2947</v>
+        <v>-1.2948</v>
       </c>
       <c r="F6" t="n">
         <v>-1.2948</v>
       </c>
       <c r="G6" t="n">
-        <v>22.356897</v>
+        <v>22.356076</v>
       </c>
       <c r="H6" t="n">
-        <v>22.354297</v>
+        <v>22.353897</v>
       </c>
       <c r="I6" t="n">
-        <v>27.4095</v>
+        <v>27.4084</v>
       </c>
       <c r="J6" t="n">
-        <v>27.406</v>
+        <v>27.4055</v>
       </c>
       <c r="K6" t="n">
-        <v>372.32</v>
+        <v>372.331</v>
       </c>
       <c r="L6" t="n">
-        <v>362.021</v>
+        <v>361.939</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1962</v>
+        <v>0.1978</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5924</v>
+        <v>4.5922</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0998</v>
+        <v>0.0997</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0998</v>
+        <v>0.0997</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0833</v>
+        <v>0.0834</v>
       </c>
       <c r="R6" t="n">
         <v>0.0329</v>
       </c>
       <c r="S6" t="n">
-        <v>4970</v>
+        <v>4972</v>
       </c>
       <c r="T6" t="n">
-        <v>3.4505</v>
+        <v>3.452</v>
       </c>
       <c r="U6" t="n">
-        <v>32.54</v>
+        <v>32.28</v>
       </c>
       <c r="V6" t="n">
-        <v>2.5794</v>
+        <v>2.5795</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2334</v>
+        <v>2.233</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1004,7 +1004,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7.917</v>
+        <v>7.915</v>
       </c>
       <c r="B7" t="n">
         <v>74.4615</v>
@@ -1016,64 +1016,64 @@
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2992</v>
+        <v>-1.2989</v>
       </c>
       <c r="F7" t="n">
         <v>-1.2975</v>
       </c>
       <c r="G7" t="n">
-        <v>22.33185</v>
+        <v>22.335334</v>
       </c>
       <c r="H7" t="n">
-        <v>22.339261</v>
+        <v>22.341177</v>
       </c>
       <c r="I7" t="n">
-        <v>27.3795</v>
+        <v>27.3839</v>
       </c>
       <c r="J7" t="n">
-        <v>27.3879</v>
+        <v>27.3905</v>
       </c>
       <c r="K7" t="n">
-        <v>372.534</v>
+        <v>372.485</v>
       </c>
       <c r="L7" t="n">
-        <v>361.526</v>
+        <v>361.498</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2017</v>
+        <v>0.2074</v>
       </c>
       <c r="N7" t="n">
         <v>4.5925</v>
       </c>
       <c r="O7" t="n">
-        <v>0.101</v>
+        <v>0.1013</v>
       </c>
       <c r="P7" t="n">
-        <v>0.101</v>
+        <v>0.1013</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0832</v>
+        <v>0.0833</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0331</v>
+        <v>0.0333</v>
       </c>
       <c r="S7" t="n">
-        <v>5050</v>
+        <v>5053</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5063</v>
+        <v>3.5083</v>
       </c>
       <c r="U7" t="n">
-        <v>31.83</v>
+        <v>31.42</v>
       </c>
       <c r="V7" t="n">
-        <v>2.5796</v>
+        <v>2.5794</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2304</v>
+        <v>2.2303</v>
       </c>
       <c r="X7" t="n">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1096,7 +1096,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8.906</v>
+        <v>8.909</v>
       </c>
       <c r="B8" t="n">
         <v>74.4615</v>
@@ -1108,40 +1108,40 @@
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2946</v>
+        <v>-1.294</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2945</v>
+        <v>-1.2938</v>
       </c>
       <c r="G8" t="n">
-        <v>22.350735</v>
+        <v>22.354301</v>
       </c>
       <c r="H8" t="n">
-        <v>22.349995</v>
+        <v>22.354176</v>
       </c>
       <c r="I8" t="n">
-        <v>27.4001</v>
+        <v>27.4042</v>
       </c>
       <c r="J8" t="n">
-        <v>27.399</v>
+        <v>27.4038</v>
       </c>
       <c r="K8" t="n">
-        <v>372.609</v>
+        <v>372.61</v>
       </c>
       <c r="L8" t="n">
-        <v>361.667</v>
+        <v>361.605</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1725</v>
+        <v>0.1731</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5924</v>
+        <v>4.5923</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1009</v>
+        <v>0.1008</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1009</v>
+        <v>0.1008</v>
       </c>
       <c r="Q8" t="n">
         <v>0.0833</v>
@@ -1150,22 +1150,22 @@
         <v>0.0319</v>
       </c>
       <c r="S8" t="n">
-        <v>5105</v>
+        <v>5106</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5444</v>
+        <v>3.545</v>
       </c>
       <c r="U8" t="n">
-        <v>32.47</v>
+        <v>32.17</v>
       </c>
       <c r="V8" t="n">
-        <v>2.5803</v>
+        <v>2.5804</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2312</v>
+        <v>2.231</v>
       </c>
       <c r="X8" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9.896</v>
+        <v>9.893</v>
       </c>
       <c r="B9" t="n">
         <v>74.4615</v>
@@ -1200,64 +1200,64 @@
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2834</v>
+        <v>-1.283</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2826</v>
+        <v>-1.2824</v>
       </c>
       <c r="G9" t="n">
-        <v>22.423474</v>
+        <v>22.426282</v>
       </c>
       <c r="H9" t="n">
-        <v>22.423948</v>
+        <v>22.424546</v>
       </c>
       <c r="I9" t="n">
-        <v>27.4869</v>
+        <v>27.4899</v>
       </c>
       <c r="J9" t="n">
-        <v>27.4867</v>
+        <v>27.487</v>
       </c>
       <c r="K9" t="n">
-        <v>372.251</v>
+        <v>372.186</v>
       </c>
       <c r="L9" t="n">
-        <v>361.574</v>
+        <v>361.589</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1928</v>
+        <v>0.198</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5921</v>
+        <v>4.5923</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1009</v>
+        <v>0.1006</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1009</v>
+        <v>0.1006</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0835</v>
+        <v>0.0833</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0327</v>
+        <v>0.033</v>
       </c>
       <c r="S9" t="n">
-        <v>5178</v>
+        <v>5181</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5949</v>
+        <v>3.597</v>
       </c>
       <c r="U9" t="n">
-        <v>32.78</v>
+        <v>32.68</v>
       </c>
       <c r="V9" t="n">
-        <v>2.5802</v>
+        <v>2.5799</v>
       </c>
       <c r="W9" t="n">
-        <v>2.2323</v>
+        <v>2.2324</v>
       </c>
       <c r="X9" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10.886</v>
+        <v>10.887</v>
       </c>
       <c r="B10" t="n">
         <v>74.4615</v>
@@ -1292,34 +1292,34 @@
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2776</v>
+        <v>-1.2778</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2777</v>
+        <v>-1.2778</v>
       </c>
       <c r="G10" t="n">
-        <v>22.452106</v>
+        <v>22.45098</v>
       </c>
       <c r="H10" t="n">
-        <v>22.449184</v>
+        <v>22.44879</v>
       </c>
       <c r="I10" t="n">
-        <v>27.5193</v>
+        <v>27.5175</v>
       </c>
       <c r="J10" t="n">
-        <v>27.5155</v>
+        <v>27.5147</v>
       </c>
       <c r="K10" t="n">
-        <v>372.251</v>
+        <v>372.281</v>
       </c>
       <c r="L10" t="n">
-        <v>361.298</v>
+        <v>361.316</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1975</v>
+        <v>0.1964</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5907</v>
+        <v>4.5908</v>
       </c>
       <c r="O10" t="n">
         <v>0.1017</v>
@@ -1328,7 +1328,7 @@
         <v>0.1017</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0847</v>
+        <v>0.0846</v>
       </c>
       <c r="R10" t="n">
         <v>0.0329</v>
@@ -1337,19 +1337,19 @@
         <v>5227</v>
       </c>
       <c r="T10" t="n">
-        <v>3.6289</v>
+        <v>3.6294</v>
       </c>
       <c r="U10" t="n">
-        <v>32.81</v>
+        <v>32.4</v>
       </c>
       <c r="V10" t="n">
-        <v>2.5808</v>
+        <v>2.5809</v>
       </c>
       <c r="W10" t="n">
-        <v>2.2314</v>
+        <v>2.2315</v>
       </c>
       <c r="X10" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1372,7 +1372,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11.875</v>
+        <v>11.876</v>
       </c>
       <c r="B11" t="n">
         <v>74.46151</v>
@@ -1384,64 +1384,64 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.283</v>
+        <v>-1.282</v>
       </c>
       <c r="F11" t="n">
         <v>-1.2786</v>
       </c>
       <c r="G11" t="n">
-        <v>22.427443</v>
+        <v>22.432814</v>
       </c>
       <c r="H11" t="n">
-        <v>22.445987</v>
+        <v>22.446379</v>
       </c>
       <c r="I11" t="n">
-        <v>27.4907</v>
+        <v>27.4967</v>
       </c>
       <c r="J11" t="n">
-        <v>27.5115</v>
+        <v>27.5118</v>
       </c>
       <c r="K11" t="n">
-        <v>372.543</v>
+        <v>372.551</v>
       </c>
       <c r="L11" t="n">
-        <v>361.386</v>
+        <v>361.341</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2135</v>
+        <v>0.2155</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5919</v>
+        <v>4.592</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1017</v>
+        <v>0.1016</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1017</v>
+        <v>0.1016</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0838</v>
+        <v>0.0836</v>
       </c>
       <c r="R11" t="n">
         <v>0.0336</v>
       </c>
       <c r="S11" t="n">
-        <v>5279</v>
+        <v>5282</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6654</v>
+        <v>3.6673</v>
       </c>
       <c r="U11" t="n">
-        <v>26.12</v>
+        <v>25.89</v>
       </c>
       <c r="V11" t="n">
-        <v>2.5814</v>
+        <v>2.5816</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2315</v>
+        <v>2.2313</v>
       </c>
       <c r="X11" t="n">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>12.865</v>
+        <v>12.864</v>
       </c>
       <c r="B12" t="n">
         <v>74.46152</v>
@@ -1476,43 +1476,43 @@
         <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2724</v>
+        <v>-1.2721</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2738</v>
+        <v>-1.2733</v>
       </c>
       <c r="G12" t="n">
-        <v>22.479875</v>
+        <v>22.481599</v>
       </c>
       <c r="H12" t="n">
-        <v>22.470071</v>
+        <v>22.472888</v>
       </c>
       <c r="I12" t="n">
-        <v>27.5506</v>
+        <v>27.5523</v>
       </c>
       <c r="J12" t="n">
-        <v>27.5389</v>
+        <v>27.5418</v>
       </c>
       <c r="K12" t="n">
-        <v>372.341</v>
+        <v>372.313</v>
       </c>
       <c r="L12" t="n">
-        <v>361.527</v>
+        <v>361.473</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1965</v>
+        <v>0.1968</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5923</v>
+        <v>4.5922</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1019</v>
+        <v>0.1021</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1019</v>
+        <v>0.1021</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0834</v>
+        <v>0.0835</v>
       </c>
       <c r="R12" t="n">
         <v>0.0329</v>
@@ -1521,19 +1521,19 @@
         <v>5342</v>
       </c>
       <c r="T12" t="n">
-        <v>3.7092</v>
+        <v>3.7087</v>
       </c>
       <c r="U12" t="n">
-        <v>26.26</v>
+        <v>25.3</v>
       </c>
       <c r="V12" t="n">
-        <v>2.5816</v>
+        <v>2.5815</v>
       </c>
       <c r="W12" t="n">
-        <v>2.2326</v>
+        <v>2.2324</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -1556,7 +1556,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>13.854</v>
+        <v>13.856</v>
       </c>
       <c r="B13" t="n">
         <v>74.46152</v>
@@ -1568,64 +1568,64 @@
         <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2743</v>
+        <v>-1.2749</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2738</v>
+        <v>-1.2744</v>
       </c>
       <c r="G13" t="n">
-        <v>22.472479</v>
+        <v>22.470076</v>
       </c>
       <c r="H13" t="n">
-        <v>22.471398</v>
+        <v>22.468739</v>
       </c>
       <c r="I13" t="n">
-        <v>27.542</v>
+        <v>27.5391</v>
       </c>
       <c r="J13" t="n">
-        <v>27.5401</v>
+        <v>27.5369</v>
       </c>
       <c r="K13" t="n">
-        <v>372.384</v>
+        <v>372.407</v>
       </c>
       <c r="L13" t="n">
-        <v>360.999</v>
+        <v>361.043</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1944</v>
+        <v>0.1972</v>
       </c>
       <c r="N13" t="n">
         <v>4.5919</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1025</v>
+        <v>0.1024</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1025</v>
+        <v>0.1024</v>
       </c>
       <c r="Q13" t="n">
         <v>0.0838</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0328</v>
+        <v>0.0329</v>
       </c>
       <c r="S13" t="n">
-        <v>5388</v>
+        <v>5390</v>
       </c>
       <c r="T13" t="n">
-        <v>3.741</v>
+        <v>3.7422</v>
       </c>
       <c r="U13" t="n">
-        <v>17.78</v>
+        <v>17.08</v>
       </c>
       <c r="V13" t="n">
         <v>2.5813</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2299</v>
+        <v>2.23</v>
       </c>
       <c r="X13" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>14.844</v>
+        <v>14.841</v>
       </c>
       <c r="B14" t="n">
         <v>74.46152</v>
@@ -1660,31 +1660,31 @@
         <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.2811</v>
+        <v>-1.2816</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2805</v>
+        <v>-1.2808</v>
       </c>
       <c r="G14" t="n">
-        <v>22.450021</v>
+        <v>22.447224</v>
       </c>
       <c r="H14" t="n">
-        <v>22.452336</v>
+        <v>22.450907</v>
       </c>
       <c r="I14" t="n">
-        <v>27.5176</v>
+        <v>27.5144</v>
       </c>
       <c r="J14" t="n">
-        <v>27.5202</v>
+        <v>27.5186</v>
       </c>
       <c r="K14" t="n">
-        <v>372.582</v>
+        <v>372.602</v>
       </c>
       <c r="L14" t="n">
-        <v>361.395</v>
+        <v>361.378</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1928</v>
+        <v>0.1937</v>
       </c>
       <c r="N14" t="n">
         <v>4.5911</v>
@@ -1696,28 +1696,28 @@
         <v>0.102</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0844</v>
+        <v>0.0845</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0327</v>
+        <v>0.0328</v>
       </c>
       <c r="S14" t="n">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="T14" t="n">
-        <v>3.782</v>
+        <v>3.7827</v>
       </c>
       <c r="U14" t="n">
-        <v>12.14</v>
+        <v>12.17</v>
       </c>
       <c r="V14" t="n">
         <v>2.5813</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2309</v>
+        <v>2.2308</v>
       </c>
       <c r="X14" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15.834</v>
+        <v>15.836</v>
       </c>
       <c r="B15" t="n">
         <v>74.46152</v>
@@ -1752,64 +1752,64 @@
         <v>16</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.2717</v>
+        <v>-1.2716</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2714</v>
+        <v>-1.2707</v>
       </c>
       <c r="G15" t="n">
-        <v>22.486033</v>
+        <v>22.489235</v>
       </c>
       <c r="H15" t="n">
-        <v>22.487504</v>
+        <v>22.494067</v>
       </c>
       <c r="I15" t="n">
-        <v>27.5567</v>
+        <v>27.5606</v>
       </c>
       <c r="J15" t="n">
-        <v>27.5584</v>
+        <v>27.5662</v>
       </c>
       <c r="K15" t="n">
-        <v>372.213</v>
+        <v>372.164</v>
       </c>
       <c r="L15" t="n">
-        <v>361.152</v>
+        <v>361.308</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1889</v>
+        <v>0.1847</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5927</v>
+        <v>4.5926</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1024</v>
+        <v>0.1027</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1024</v>
+        <v>0.1027</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.083</v>
+        <v>0.0831</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0326</v>
+        <v>0.0324</v>
       </c>
       <c r="S15" t="n">
-        <v>5490</v>
+        <v>5492</v>
       </c>
       <c r="T15" t="n">
-        <v>3.8115</v>
+        <v>3.8131</v>
       </c>
       <c r="U15" t="n">
-        <v>8.75</v>
+        <v>10.39</v>
       </c>
       <c r="V15" t="n">
-        <v>2.5802</v>
+        <v>2.58</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2305</v>
+        <v>2.2314</v>
       </c>
       <c r="X15" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -1832,7 +1832,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16.823</v>
+        <v>16.821</v>
       </c>
       <c r="B16" t="n">
         <v>74.46153</v>
@@ -1844,64 +1844,64 @@
         <v>17</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2221</v>
+        <v>-1.2206</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2266</v>
+        <v>-1.2248</v>
       </c>
       <c r="G16" t="n">
-        <v>22.803732</v>
+        <v>22.816755</v>
       </c>
       <c r="H16" t="n">
-        <v>22.763941</v>
+        <v>22.779247</v>
       </c>
       <c r="I16" t="n">
-        <v>27.936</v>
+        <v>27.9504</v>
       </c>
       <c r="J16" t="n">
-        <v>27.8869</v>
+        <v>27.9042</v>
       </c>
       <c r="K16" t="n">
-        <v>370.517</v>
+        <v>370.415</v>
       </c>
       <c r="L16" t="n">
-        <v>360.403</v>
+        <v>360.397</v>
       </c>
       <c r="M16" t="n">
-        <v>0.195</v>
+        <v>0.1962</v>
       </c>
       <c r="N16" t="n">
-        <v>4.593</v>
+        <v>4.5931</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1037</v>
+        <v>0.1041</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1037</v>
+        <v>0.1041</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0828</v>
+        <v>0.0827</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0328</v>
+        <v>0.0329</v>
       </c>
       <c r="S16" t="n">
-        <v>5556</v>
+        <v>5559</v>
       </c>
       <c r="T16" t="n">
-        <v>3.8579</v>
+        <v>3.8596</v>
       </c>
       <c r="U16" t="n">
-        <v>37.2</v>
+        <v>39.02</v>
       </c>
       <c r="V16" t="n">
-        <v>2.5798</v>
+        <v>2.5796</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2335</v>
+        <v>2.2338</v>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -1936,34 +1936,34 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1824</v>
+        <v>-1.1809</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1893</v>
+        <v>-1.1883</v>
       </c>
       <c r="G17" t="n">
-        <v>23.081143</v>
+        <v>23.090631</v>
       </c>
       <c r="H17" t="n">
-        <v>23.04147</v>
+        <v>23.049944</v>
       </c>
       <c r="I17" t="n">
-        <v>28.2701</v>
+        <v>28.2789</v>
       </c>
       <c r="J17" t="n">
-        <v>28.2235</v>
+        <v>28.2315</v>
       </c>
       <c r="K17" t="n">
-        <v>369.645</v>
+        <v>369.621</v>
       </c>
       <c r="L17" t="n">
-        <v>358.95</v>
+        <v>358.953</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2921</v>
+        <v>0.2927</v>
       </c>
       <c r="N17" t="n">
-        <v>4.5909</v>
+        <v>4.5908</v>
       </c>
       <c r="O17" t="n">
         <v>0.1047</v>
@@ -1972,7 +1972,7 @@
         <v>0.1047</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0846</v>
+        <v>0.0847</v>
       </c>
       <c r="R17" t="n">
         <v>0.0367</v>
@@ -1981,19 +1981,19 @@
         <v>5607</v>
       </c>
       <c r="T17" t="n">
-        <v>3.893</v>
+        <v>3.8932</v>
       </c>
       <c r="U17" t="n">
-        <v>39.13</v>
+        <v>39.3</v>
       </c>
       <c r="V17" t="n">
-        <v>2.5826</v>
+        <v>2.5828</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2329</v>
+        <v>2.233</v>
       </c>
       <c r="X17" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>18.802</v>
+        <v>18.804</v>
       </c>
       <c r="B18" t="n">
         <v>74.46154</v>
@@ -2028,28 +2028,28 @@
         <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1472</v>
+        <v>-1.1456</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1489</v>
+        <v>-1.1473</v>
       </c>
       <c r="G18" t="n">
-        <v>23.229423</v>
+        <v>23.249382</v>
       </c>
       <c r="H18" t="n">
-        <v>23.221836</v>
+        <v>23.239259</v>
       </c>
       <c r="I18" t="n">
-        <v>28.435</v>
+        <v>28.4573</v>
       </c>
       <c r="J18" t="n">
-        <v>28.4265</v>
+        <v>28.4453</v>
       </c>
       <c r="K18" t="n">
-        <v>369.407</v>
+        <v>369.346</v>
       </c>
       <c r="L18" t="n">
-        <v>358.494</v>
+        <v>358.475</v>
       </c>
       <c r="M18" t="n">
         <v>0.333</v>
@@ -2058,34 +2058,34 @@
         <v>4.5882</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1053</v>
+        <v>0.1052</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1053</v>
+        <v>0.1052</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.087</v>
+        <v>0.0869</v>
       </c>
       <c r="R18" t="n">
         <v>0.0384</v>
       </c>
       <c r="S18" t="n">
-        <v>5653</v>
+        <v>5655</v>
       </c>
       <c r="T18" t="n">
-        <v>3.9252</v>
+        <v>3.9267</v>
       </c>
       <c r="U18" t="n">
-        <v>37.29</v>
+        <v>37.1</v>
       </c>
       <c r="V18" t="n">
-        <v>2.586</v>
+        <v>2.5861</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2353</v>
+        <v>2.2356</v>
       </c>
       <c r="X18" t="n">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>19.792</v>
+        <v>19.79</v>
       </c>
       <c r="B19" t="n">
         <v>74.46154</v>
@@ -2120,40 +2120,40 @@
         <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1299</v>
+        <v>-1.1289</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.128</v>
+        <v>-1.1269</v>
       </c>
       <c r="G19" t="n">
-        <v>23.589525</v>
+        <v>23.602212</v>
       </c>
       <c r="H19" t="n">
-        <v>23.588365</v>
+        <v>23.601634</v>
       </c>
       <c r="I19" t="n">
-        <v>28.9009</v>
+        <v>28.9146</v>
       </c>
       <c r="J19" t="n">
-        <v>28.8975</v>
+        <v>28.9119</v>
       </c>
       <c r="K19" t="n">
-        <v>368.751</v>
+        <v>368.725</v>
       </c>
       <c r="L19" t="n">
-        <v>357.942</v>
+        <v>357.919</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4169</v>
+        <v>0.4174</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5857</v>
+        <v>4.5858</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1083</v>
+        <v>0.1085</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1083</v>
+        <v>0.1085</v>
       </c>
       <c r="Q19" t="n">
         <v>0.0891</v>
@@ -2162,22 +2162,22 @@
         <v>0.0417</v>
       </c>
       <c r="S19" t="n">
-        <v>5721</v>
+        <v>5723</v>
       </c>
       <c r="T19" t="n">
-        <v>3.9726</v>
+        <v>3.9738</v>
       </c>
       <c r="U19" t="n">
-        <v>15.57</v>
+        <v>14.99</v>
       </c>
       <c r="V19" t="n">
-        <v>2.5908</v>
+        <v>2.5909</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2399</v>
+        <v>2.2401</v>
       </c>
       <c r="X19" t="n">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2200,7 +2200,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20.782</v>
+        <v>20.781</v>
       </c>
       <c r="B20" t="n">
         <v>74.46154</v>
@@ -2212,34 +2212,34 @@
         <v>21</v>
       </c>
       <c r="E20" t="n">
+        <v>-1.1792</v>
+      </c>
+      <c r="F20" t="n">
         <v>-1.1785</v>
       </c>
-      <c r="F20" t="n">
-        <v>-1.1779</v>
-      </c>
       <c r="G20" t="n">
-        <v>23.581202</v>
+        <v>23.581649</v>
       </c>
       <c r="H20" t="n">
-        <v>23.579473</v>
+        <v>23.579937</v>
       </c>
       <c r="I20" t="n">
-        <v>28.9362</v>
+        <v>28.9372</v>
       </c>
       <c r="J20" t="n">
-        <v>28.9332</v>
+        <v>28.9342</v>
       </c>
       <c r="K20" t="n">
-        <v>369.872</v>
+        <v>369.881</v>
       </c>
       <c r="L20" t="n">
-        <v>358.807</v>
+        <v>358.853</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4968</v>
+        <v>0.4948</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5809</v>
+        <v>4.5808</v>
       </c>
       <c r="O20" t="n">
         <v>0.1112</v>
@@ -2248,28 +2248,28 @@
         <v>0.1112</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.0934</v>
+        <v>0.0935</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0449</v>
+        <v>0.0448</v>
       </c>
       <c r="S20" t="n">
-        <v>5769</v>
+        <v>5770</v>
       </c>
       <c r="T20" t="n">
-        <v>4.0054</v>
+        <v>4.0059</v>
       </c>
       <c r="U20" t="n">
-        <v>9.59</v>
+        <v>9.44</v>
       </c>
       <c r="V20" t="n">
         <v>2.5944</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2417</v>
+        <v>2.2419</v>
       </c>
       <c r="X20" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -2292,46 +2292,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>21.771</v>
+        <v>21.772</v>
       </c>
       <c r="B21" t="n">
         <v>74.46154</v>
       </c>
       <c r="C21" t="n">
-        <v>169.90178</v>
+        <v>169.90179</v>
       </c>
       <c r="D21" t="n">
         <v>22</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1808</v>
+        <v>-1.1784</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1811</v>
+        <v>-1.1787</v>
       </c>
       <c r="G21" t="n">
-        <v>23.629221</v>
+        <v>23.63279</v>
       </c>
       <c r="H21" t="n">
-        <v>23.626262</v>
+        <v>23.629793</v>
       </c>
       <c r="I21" t="n">
-        <v>29.0024</v>
+        <v>29.0046</v>
       </c>
       <c r="J21" t="n">
-        <v>28.9987</v>
+        <v>29.0009</v>
       </c>
       <c r="K21" t="n">
-        <v>369.685</v>
+        <v>369.582</v>
       </c>
       <c r="L21" t="n">
-        <v>359.195</v>
+        <v>359.172</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4694</v>
+        <v>0.4649</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5821</v>
+        <v>4.5826</v>
       </c>
       <c r="O21" t="n">
         <v>0.1109</v>
@@ -2340,28 +2340,28 @@
         <v>0.1109</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.0923</v>
+        <v>0.0919</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0438</v>
+        <v>0.0436</v>
       </c>
       <c r="S21" t="n">
-        <v>5817</v>
+        <v>5819</v>
       </c>
       <c r="T21" t="n">
-        <v>4.039</v>
+        <v>4.0405</v>
       </c>
       <c r="U21" t="n">
-        <v>11.87</v>
+        <v>11.89</v>
       </c>
       <c r="V21" t="n">
-        <v>2.594</v>
+        <v>2.5936</v>
       </c>
       <c r="W21" t="n">
-        <v>2.244</v>
+        <v>2.2441</v>
       </c>
       <c r="X21" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2384,67 +2384,67 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>22.76</v>
+        <v>22.758</v>
       </c>
       <c r="B22" t="n">
         <v>74.46155</v>
       </c>
       <c r="C22" t="n">
-        <v>169.90182</v>
+        <v>169.90183</v>
       </c>
       <c r="D22" t="n">
         <v>23</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1868</v>
+        <v>-1.1864</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1859</v>
+        <v>-1.1854</v>
       </c>
       <c r="G22" t="n">
-        <v>23.684454</v>
+        <v>23.68549</v>
       </c>
       <c r="H22" t="n">
-        <v>23.682555</v>
+        <v>23.683693</v>
       </c>
       <c r="I22" t="n">
-        <v>29.082</v>
+        <v>29.0831</v>
       </c>
       <c r="J22" t="n">
-        <v>29.0786</v>
+        <v>29.0797</v>
       </c>
       <c r="K22" t="n">
-        <v>369.051</v>
+        <v>369.03</v>
       </c>
       <c r="L22" t="n">
-        <v>358.588</v>
+        <v>358.585</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3772</v>
+        <v>0.375</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5883</v>
+        <v>4.5884</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1097</v>
+        <v>0.1099</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1097</v>
+        <v>0.1099</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.0869</v>
+        <v>0.0868</v>
       </c>
       <c r="R22" t="n">
-        <v>0.0401</v>
+        <v>0.04</v>
       </c>
       <c r="S22" t="n">
-        <v>5880</v>
+        <v>5881</v>
       </c>
       <c r="T22" t="n">
-        <v>4.0826</v>
+        <v>4.0834</v>
       </c>
       <c r="U22" t="n">
-        <v>20.78</v>
+        <v>20.32</v>
       </c>
       <c r="V22" t="n">
         <v>2.591</v>
@@ -2453,7 +2453,7 @@
         <v>2.2418</v>
       </c>
       <c r="X22" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -2476,7 +2476,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>23.75</v>
+        <v>23.752</v>
       </c>
       <c r="B23" t="n">
         <v>74.46156</v>
@@ -2488,64 +2488,64 @@
         <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2316</v>
+        <v>-1.2358</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2305</v>
+        <v>-1.2348</v>
       </c>
       <c r="G23" t="n">
-        <v>23.698842</v>
+        <v>23.69626</v>
       </c>
       <c r="H23" t="n">
-        <v>23.697462</v>
+        <v>23.694856</v>
       </c>
       <c r="I23" t="n">
-        <v>29.1444</v>
+        <v>29.1467</v>
       </c>
       <c r="J23" t="n">
-        <v>29.1415</v>
+        <v>29.1438</v>
       </c>
       <c r="K23" t="n">
-        <v>370.816</v>
+        <v>370.888</v>
       </c>
       <c r="L23" t="n">
-        <v>359.737</v>
+        <v>359.874</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3697</v>
+        <v>0.3764</v>
       </c>
       <c r="N23" t="n">
-        <v>4.5975</v>
+        <v>4.598</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1113</v>
+        <v>0.1112</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1113</v>
+        <v>0.1112</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.0789</v>
+        <v>0.0784</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0398</v>
+        <v>0.0401</v>
       </c>
       <c r="S23" t="n">
-        <v>5925</v>
+        <v>5928</v>
       </c>
       <c r="T23" t="n">
-        <v>4.1142</v>
+        <v>4.1157</v>
       </c>
       <c r="U23" t="n">
-        <v>10.64</v>
+        <v>10</v>
       </c>
       <c r="V23" t="n">
-        <v>2.5989</v>
+        <v>2.5991</v>
       </c>
       <c r="W23" t="n">
-        <v>2.2455</v>
+        <v>2.246</v>
       </c>
       <c r="X23" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>24.74</v>
+        <v>24.736</v>
       </c>
       <c r="B24" t="n">
         <v>74.46156</v>
@@ -2580,64 +2580,64 @@
         <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2659</v>
+        <v>-1.2683</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2658</v>
+        <v>-1.2683</v>
       </c>
       <c r="G24" t="n">
-        <v>23.720357</v>
+        <v>23.718551</v>
       </c>
       <c r="H24" t="n">
-        <v>23.718682</v>
+        <v>23.716831</v>
       </c>
       <c r="I24" t="n">
-        <v>29.2063</v>
+        <v>29.2082</v>
       </c>
       <c r="J24" t="n">
-        <v>29.204</v>
+        <v>29.2059</v>
       </c>
       <c r="K24" t="n">
-        <v>371.627</v>
+        <v>371.702</v>
       </c>
       <c r="L24" t="n">
-        <v>361.258</v>
+        <v>361.347</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3726</v>
+        <v>0.3792</v>
       </c>
       <c r="N24" t="n">
-        <v>4.6065</v>
+        <v>4.6071</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1103</v>
+        <v>0.1102</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1103</v>
+        <v>0.1102</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.071</v>
+        <v>0.0705</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0399</v>
+        <v>0.0402</v>
       </c>
       <c r="S24" t="n">
-        <v>5993</v>
+        <v>5995</v>
       </c>
       <c r="T24" t="n">
-        <v>4.1613</v>
+        <v>4.1625</v>
       </c>
       <c r="U24" t="n">
-        <v>30.47</v>
+        <v>31.74</v>
       </c>
       <c r="V24" t="n">
-        <v>2.6021</v>
+        <v>2.6024</v>
       </c>
       <c r="W24" t="n">
-        <v>2.2516</v>
+        <v>2.252</v>
       </c>
       <c r="X24" t="n">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -2672,64 +2672,64 @@
         <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.2576</v>
+        <v>-1.2574</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2574</v>
+        <v>-1.2572</v>
       </c>
       <c r="G25" t="n">
-        <v>23.762501</v>
+        <v>23.762495</v>
       </c>
       <c r="H25" t="n">
-        <v>23.760697</v>
+        <v>23.760699</v>
       </c>
       <c r="I25" t="n">
-        <v>29.2545</v>
+        <v>29.2555</v>
       </c>
       <c r="J25" t="n">
-        <v>29.2519</v>
+        <v>29.2529</v>
       </c>
       <c r="K25" t="n">
-        <v>370.494</v>
+        <v>370.455</v>
       </c>
       <c r="L25" t="n">
-        <v>360.259</v>
+        <v>360.257</v>
       </c>
       <c r="M25" t="n">
-        <v>0.348</v>
+        <v>0.3499</v>
       </c>
       <c r="N25" t="n">
-        <v>4.6104</v>
+        <v>4.6103</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1082</v>
+        <v>0.1083</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1082</v>
+        <v>0.1083</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0676</v>
+        <v>0.0677</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0389</v>
+        <v>0.039</v>
       </c>
       <c r="S25" t="n">
-        <v>6039</v>
+        <v>6040</v>
       </c>
       <c r="T25" t="n">
-        <v>4.1933</v>
+        <v>4.1939</v>
       </c>
       <c r="U25" t="n">
-        <v>23.49</v>
+        <v>22.46</v>
       </c>
       <c r="V25" t="n">
-        <v>2.5967</v>
+        <v>2.5965</v>
       </c>
       <c r="W25" t="n">
         <v>2.2477</v>
       </c>
       <c r="X25" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26.719</v>
+        <v>26.72</v>
       </c>
       <c r="B26" t="n">
         <v>74.46156</v>
@@ -2764,34 +2764,34 @@
         <v>27</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.2592</v>
+        <v>-1.2594</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.2588</v>
+        <v>-1.2591</v>
       </c>
       <c r="G26" t="n">
-        <v>23.78806</v>
+        <v>23.788161</v>
       </c>
       <c r="H26" t="n">
-        <v>23.786643</v>
+        <v>23.786751</v>
       </c>
       <c r="I26" t="n">
-        <v>29.29</v>
+        <v>29.2913</v>
       </c>
       <c r="J26" t="n">
-        <v>29.2878</v>
+        <v>29.2891</v>
       </c>
       <c r="K26" t="n">
-        <v>369.778</v>
+        <v>369.727</v>
       </c>
       <c r="L26" t="n">
-        <v>360.047</v>
+        <v>360.058</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3307</v>
+        <v>0.3298</v>
       </c>
       <c r="N26" t="n">
-        <v>4.6145</v>
+        <v>4.6147</v>
       </c>
       <c r="O26" t="n">
         <v>0.1106</v>
@@ -2800,28 +2800,28 @@
         <v>0.1106</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.0641</v>
+        <v>0.0638</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0383</v>
+        <v>0.0382</v>
       </c>
       <c r="S26" t="n">
-        <v>6090</v>
+        <v>6092</v>
       </c>
       <c r="T26" t="n">
-        <v>4.2283</v>
+        <v>4.2299</v>
       </c>
       <c r="U26" t="n">
-        <v>3.09</v>
+        <v>2.63</v>
       </c>
       <c r="V26" t="n">
-        <v>2.5928</v>
+        <v>2.5925</v>
       </c>
       <c r="W26" t="n">
-        <v>2.2468</v>
+        <v>2.2469</v>
       </c>
       <c r="X26" t="n">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>27.708</v>
+        <v>27.706</v>
       </c>
       <c r="B27" t="n">
         <v>74.46156</v>
@@ -2856,31 +2856,31 @@
         <v>28</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.2781</v>
+        <v>-1.2787</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.2781</v>
+        <v>-1.2787</v>
       </c>
       <c r="G27" t="n">
-        <v>23.794117</v>
+        <v>23.793122</v>
       </c>
       <c r="H27" t="n">
-        <v>23.792772</v>
+        <v>23.791823</v>
       </c>
       <c r="I27" t="n">
-        <v>29.3162</v>
+        <v>29.3167</v>
       </c>
       <c r="J27" t="n">
-        <v>29.3143</v>
+        <v>29.3149</v>
       </c>
       <c r="K27" t="n">
-        <v>368.69</v>
+        <v>368.674</v>
       </c>
       <c r="L27" t="n">
-        <v>359.244</v>
+        <v>359.155</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2826</v>
+        <v>0.2887</v>
       </c>
       <c r="N27" t="n">
         <v>4.6186</v>
@@ -2895,25 +2895,25 @@
         <v>0.0606</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0363</v>
+        <v>0.0365</v>
       </c>
       <c r="S27" t="n">
-        <v>6153</v>
+        <v>6154</v>
       </c>
       <c r="T27" t="n">
-        <v>4.272</v>
+        <v>4.2729</v>
       </c>
       <c r="U27" t="n">
-        <v>11.81</v>
+        <v>11.94</v>
       </c>
       <c r="V27" t="n">
-        <v>2.5856</v>
+        <v>2.5855</v>
       </c>
       <c r="W27" t="n">
-        <v>2.2421</v>
+        <v>2.2417</v>
       </c>
       <c r="X27" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>28.697</v>
+        <v>28.698</v>
       </c>
       <c r="B28" t="n">
         <v>74.46158</v>
@@ -2948,34 +2948,34 @@
         <v>29</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.3025</v>
+        <v>-1.3032</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.3023</v>
+        <v>-1.303</v>
       </c>
       <c r="G28" t="n">
-        <v>23.790654</v>
+        <v>23.789272</v>
       </c>
       <c r="H28" t="n">
-        <v>23.789345</v>
+        <v>23.787979</v>
       </c>
       <c r="I28" t="n">
-        <v>29.3349</v>
+        <v>29.3354</v>
       </c>
       <c r="J28" t="n">
-        <v>29.333</v>
+        <v>29.3335</v>
       </c>
       <c r="K28" t="n">
-        <v>367.547</v>
+        <v>367.556</v>
       </c>
       <c r="L28" t="n">
-        <v>358.146</v>
+        <v>358.038</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2562</v>
+        <v>0.2587</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6205</v>
+        <v>4.6206</v>
       </c>
       <c r="O28" t="n">
         <v>0.1109</v>
@@ -2984,28 +2984,28 @@
         <v>0.1109</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.0589</v>
+        <v>0.0588</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0352</v>
+        <v>0.0353</v>
       </c>
       <c r="S28" t="n">
-        <v>6198</v>
+        <v>6199</v>
       </c>
       <c r="T28" t="n">
-        <v>4.3033</v>
+        <v>4.3041</v>
       </c>
       <c r="U28" t="n">
-        <v>11.44</v>
+        <v>11.1</v>
       </c>
       <c r="V28" t="n">
         <v>2.5776</v>
       </c>
       <c r="W28" t="n">
-        <v>2.2356</v>
+        <v>2.235</v>
       </c>
       <c r="X28" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -3040,64 +3040,64 @@
         <v>30</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.3225</v>
+        <v>-1.3231</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.3223</v>
+        <v>-1.3229</v>
       </c>
       <c r="G29" t="n">
-        <v>23.790583</v>
+        <v>23.789373</v>
       </c>
       <c r="H29" t="n">
-        <v>23.789284</v>
+        <v>23.78809</v>
       </c>
       <c r="I29" t="n">
-        <v>29.3539</v>
+        <v>29.3546</v>
       </c>
       <c r="J29" t="n">
-        <v>29.352</v>
+        <v>29.3527</v>
       </c>
       <c r="K29" t="n">
-        <v>365.654</v>
+        <v>365.568</v>
       </c>
       <c r="L29" t="n">
-        <v>356.655</v>
+        <v>356.627</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2327</v>
+        <v>0.2273</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6253</v>
+        <v>4.6258</v>
       </c>
       <c r="O29" t="n">
-        <v>0.1116</v>
+        <v>0.1113</v>
       </c>
       <c r="P29" t="n">
-        <v>0.1116</v>
+        <v>0.1113</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0548</v>
+        <v>0.0542</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0343</v>
+        <v>0.0341</v>
       </c>
       <c r="S29" t="n">
-        <v>6255</v>
+        <v>6258</v>
       </c>
       <c r="T29" t="n">
-        <v>4.3433</v>
+        <v>4.3451</v>
       </c>
       <c r="U29" t="n">
-        <v>1.21</v>
+        <v>0.95</v>
       </c>
       <c r="V29" t="n">
-        <v>2.5656</v>
+        <v>2.5651</v>
       </c>
       <c r="W29" t="n">
-        <v>2.2274</v>
+        <v>2.2273</v>
       </c>
       <c r="X29" t="n">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>30.676</v>
+        <v>30.675</v>
       </c>
       <c r="B30" t="n">
         <v>74.46158</v>
@@ -3132,43 +3132,43 @@
         <v>31</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.3405</v>
+        <v>-1.3411</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.3404</v>
+        <v>-1.341</v>
       </c>
       <c r="G30" t="n">
-        <v>23.791735</v>
+        <v>23.790304</v>
       </c>
       <c r="H30" t="n">
-        <v>23.790518</v>
+        <v>23.789064</v>
       </c>
       <c r="I30" t="n">
-        <v>29.3726</v>
+        <v>29.3731</v>
       </c>
       <c r="J30" t="n">
-        <v>29.3708</v>
+        <v>29.3713</v>
       </c>
       <c r="K30" t="n">
-        <v>364.959</v>
+        <v>364.967</v>
       </c>
       <c r="L30" t="n">
-        <v>355.404</v>
+        <v>355.449</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1806</v>
+        <v>0.1811</v>
       </c>
       <c r="N30" t="n">
-        <v>4.6298</v>
+        <v>4.6297</v>
       </c>
       <c r="O30" t="n">
-        <v>0.1106</v>
+        <v>0.1108</v>
       </c>
       <c r="P30" t="n">
-        <v>0.1106</v>
+        <v>0.1108</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.0508</v>
+        <v>0.0509</v>
       </c>
       <c r="R30" t="n">
         <v>0.0322</v>
@@ -3177,19 +3177,19 @@
         <v>6315</v>
       </c>
       <c r="T30" t="n">
-        <v>4.3846</v>
+        <v>4.385</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="V30" t="n">
         <v>2.5606</v>
       </c>
       <c r="W30" t="n">
-        <v>2.2205</v>
+        <v>2.2207</v>
       </c>
       <c r="X30" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -3212,7 +3212,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31.666</v>
+        <v>31.668</v>
       </c>
       <c r="B31" t="n">
         <v>74.46158</v>
@@ -3224,64 +3224,64 @@
         <v>32</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.3692</v>
+        <v>-1.3703</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.3693</v>
+        <v>-1.3703</v>
       </c>
       <c r="G31" t="n">
-        <v>23.789849</v>
+        <v>23.788222</v>
       </c>
       <c r="H31" t="n">
-        <v>23.788608</v>
+        <v>23.786964</v>
       </c>
       <c r="I31" t="n">
-        <v>29.3978</v>
+        <v>29.399</v>
       </c>
       <c r="J31" t="n">
-        <v>29.3962</v>
+        <v>29.3972</v>
       </c>
       <c r="K31" t="n">
-        <v>365.04</v>
+        <v>365.038</v>
       </c>
       <c r="L31" t="n">
-        <v>355.62</v>
+        <v>355.563</v>
       </c>
       <c r="M31" t="n">
-        <v>0.148</v>
+        <v>0.1465</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6302</v>
+        <v>4.6303</v>
       </c>
       <c r="O31" t="n">
-        <v>0.1119</v>
+        <v>0.1117</v>
       </c>
       <c r="P31" t="n">
-        <v>0.1119</v>
+        <v>0.1117</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0505</v>
+        <v>0.0504</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0309</v>
+        <v>0.0308</v>
       </c>
       <c r="S31" t="n">
-        <v>6359</v>
+        <v>6361</v>
       </c>
       <c r="T31" t="n">
-        <v>4.4153</v>
+        <v>4.4165</v>
       </c>
       <c r="U31" t="n">
-        <v>6.65</v>
+        <v>7.54</v>
       </c>
       <c r="V31" t="n">
-        <v>2.5593</v>
+        <v>2.5592</v>
       </c>
       <c r="W31" t="n">
-        <v>2.2202</v>
+        <v>2.2199</v>
       </c>
       <c r="X31" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -3316,34 +3316,34 @@
         <v>33</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.3818</v>
+        <v>-1.3822</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.3815</v>
+        <v>-1.382</v>
       </c>
       <c r="G32" t="n">
-        <v>23.808468</v>
+        <v>23.807945</v>
       </c>
       <c r="H32" t="n">
-        <v>23.807296</v>
+        <v>23.806761</v>
       </c>
       <c r="I32" t="n">
-        <v>29.4348</v>
+        <v>29.4364</v>
       </c>
       <c r="J32" t="n">
-        <v>29.433</v>
+        <v>29.4347</v>
       </c>
       <c r="K32" t="n">
-        <v>364.573</v>
+        <v>364.539</v>
       </c>
       <c r="L32" t="n">
-        <v>355.154</v>
+        <v>355.068</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0997</v>
+        <v>0.1026</v>
       </c>
       <c r="N32" t="n">
-        <v>4.6323</v>
+        <v>4.6324</v>
       </c>
       <c r="O32" t="n">
         <v>0.1115</v>
@@ -3352,28 +3352,28 @@
         <v>0.1115</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.0487</v>
+        <v>0.0486</v>
       </c>
       <c r="R32" t="n">
-        <v>0.029</v>
+        <v>0.0291</v>
       </c>
       <c r="S32" t="n">
-        <v>6419</v>
+        <v>6422</v>
       </c>
       <c r="T32" t="n">
-        <v>4.4572</v>
+        <v>4.4591</v>
       </c>
       <c r="U32" t="n">
-        <v>0.19</v>
+        <v>-0.13</v>
       </c>
       <c r="V32" t="n">
-        <v>2.5562</v>
+        <v>2.556</v>
       </c>
       <c r="W32" t="n">
-        <v>2.2176</v>
+        <v>2.2172</v>
       </c>
       <c r="X32" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>33.645</v>
+        <v>33.644</v>
       </c>
       <c r="B33" t="n">
         <v>74.46158</v>
@@ -3408,64 +3408,64 @@
         <v>34</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.3905</v>
+        <v>-1.3911</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.3906</v>
+        <v>-1.391</v>
       </c>
       <c r="G33" t="n">
-        <v>23.831063</v>
+        <v>23.830252</v>
       </c>
       <c r="H33" t="n">
-        <v>23.829784</v>
+        <v>23.829</v>
       </c>
       <c r="I33" t="n">
-        <v>29.4735</v>
+        <v>29.4747</v>
       </c>
       <c r="J33" t="n">
-        <v>29.4718</v>
+        <v>29.4729</v>
       </c>
       <c r="K33" t="n">
-        <v>363.381</v>
+        <v>363.33</v>
       </c>
       <c r="L33" t="n">
-        <v>354.498</v>
+        <v>354.394</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1077</v>
+        <v>0.11</v>
       </c>
       <c r="N33" t="n">
-        <v>4.6327</v>
+        <v>4.6326</v>
       </c>
       <c r="O33" t="n">
-        <v>0.1126</v>
+        <v>0.1125</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1126</v>
+        <v>0.1125</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0483</v>
+        <v>0.0484</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0293</v>
+        <v>0.0294</v>
       </c>
       <c r="S33" t="n">
-        <v>6476</v>
+        <v>6478</v>
       </c>
       <c r="T33" t="n">
-        <v>4.4968</v>
+        <v>4.4978</v>
       </c>
       <c r="U33" t="n">
-        <v>2.69</v>
+        <v>3.71</v>
       </c>
       <c r="V33" t="n">
-        <v>2.5493</v>
+        <v>2.549</v>
       </c>
       <c r="W33" t="n">
-        <v>2.2143</v>
+        <v>2.2138</v>
       </c>
       <c r="X33" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>34.634</v>
+        <v>34.635</v>
       </c>
       <c r="B34" t="n">
         <v>74.46159</v>
@@ -3500,64 +3500,64 @@
         <v>35</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.4114</v>
+        <v>-1.4119</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.4114</v>
+        <v>-1.412</v>
       </c>
       <c r="G34" t="n">
-        <v>23.850143</v>
+        <v>23.849376</v>
       </c>
       <c r="H34" t="n">
-        <v>23.849161</v>
+        <v>23.848371</v>
       </c>
       <c r="I34" t="n">
-        <v>29.5195</v>
+        <v>29.5209</v>
       </c>
       <c r="J34" t="n">
-        <v>29.5182</v>
+        <v>29.5196</v>
       </c>
       <c r="K34" t="n">
-        <v>362.749</v>
+        <v>362.714</v>
       </c>
       <c r="L34" t="n">
-        <v>353.723</v>
+        <v>353.634</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1742</v>
+        <v>0.1792</v>
       </c>
       <c r="N34" t="n">
-        <v>4.6317</v>
+        <v>4.6316</v>
       </c>
       <c r="O34" t="n">
-        <v>0.1101</v>
+        <v>0.1098</v>
       </c>
       <c r="P34" t="n">
-        <v>0.1101</v>
+        <v>0.1098</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.0492</v>
+        <v>0.0493</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0319</v>
+        <v>0.0322</v>
       </c>
       <c r="S34" t="n">
-        <v>6524</v>
+        <v>6526</v>
       </c>
       <c r="T34" t="n">
-        <v>4.5301</v>
+        <v>4.5311</v>
       </c>
       <c r="U34" t="n">
-        <v>21.85</v>
+        <v>22.61</v>
       </c>
       <c r="V34" t="n">
-        <v>2.5449</v>
+        <v>2.5447</v>
       </c>
       <c r="W34" t="n">
-        <v>2.2099</v>
+        <v>2.2094</v>
       </c>
       <c r="X34" t="n">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>35.624</v>
+        <v>35.623</v>
       </c>
       <c r="B35" t="n">
         <v>74.4616</v>
@@ -3592,64 +3592,64 @@
         <v>36</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.4355</v>
+        <v>-1.4363</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.4355</v>
+        <v>-1.4362</v>
       </c>
       <c r="G35" t="n">
-        <v>23.887964</v>
+        <v>23.888166</v>
       </c>
       <c r="H35" t="n">
-        <v>23.887026</v>
+        <v>23.887262</v>
       </c>
       <c r="I35" t="n">
-        <v>29.5941</v>
+        <v>29.5973</v>
       </c>
       <c r="J35" t="n">
-        <v>29.5928</v>
+        <v>29.596</v>
       </c>
       <c r="K35" t="n">
-        <v>360.651</v>
+        <v>360.474</v>
       </c>
       <c r="L35" t="n">
-        <v>352.112</v>
+        <v>351.994</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1795</v>
+        <v>0.176</v>
       </c>
       <c r="N35" t="n">
-        <v>4.6252</v>
+        <v>4.6249</v>
       </c>
       <c r="O35" t="n">
-        <v>0.114</v>
+        <v>0.1142</v>
       </c>
       <c r="P35" t="n">
-        <v>0.114</v>
+        <v>0.1142</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.0548</v>
+        <v>0.055</v>
       </c>
       <c r="R35" t="n">
-        <v>0.0322</v>
+        <v>0.032</v>
       </c>
       <c r="S35" t="n">
-        <v>6582</v>
+        <v>6584</v>
       </c>
       <c r="T35" t="n">
-        <v>4.5704</v>
+        <v>4.5719</v>
       </c>
       <c r="U35" t="n">
-        <v>9.63</v>
+        <v>9.32</v>
       </c>
       <c r="V35" t="n">
-        <v>2.5324</v>
+        <v>2.5314</v>
       </c>
       <c r="W35" t="n">
-        <v>2.2017</v>
+        <v>2.2011</v>
       </c>
       <c r="X35" t="n">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -3672,7 +3672,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>36.613</v>
+        <v>36.614</v>
       </c>
       <c r="B36" t="n">
         <v>74.4616</v>
@@ -3684,64 +3684,64 @@
         <v>37</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.4483</v>
+        <v>-1.4478</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.448</v>
+        <v>-1.4476</v>
       </c>
       <c r="G36" t="n">
-        <v>23.947755</v>
+        <v>23.949221</v>
       </c>
       <c r="H36" t="n">
-        <v>23.947134</v>
+        <v>23.948465</v>
       </c>
       <c r="I36" t="n">
-        <v>29.6875</v>
+        <v>29.6909</v>
       </c>
       <c r="J36" t="n">
-        <v>29.6864</v>
+        <v>29.6897</v>
       </c>
       <c r="K36" t="n">
-        <v>354.51</v>
+        <v>354.213</v>
       </c>
       <c r="L36" t="n">
-        <v>348.117</v>
+        <v>347.816</v>
       </c>
       <c r="M36" t="n">
-        <v>0.2014</v>
+        <v>0.1947</v>
       </c>
       <c r="N36" t="n">
-        <v>4.6257</v>
+        <v>4.6256</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1142</v>
+        <v>0.1145</v>
       </c>
       <c r="P36" t="n">
-        <v>0.1142</v>
+        <v>0.1145</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0544</v>
+        <v>0.0545</v>
       </c>
       <c r="R36" t="n">
-        <v>0.033</v>
+        <v>0.0328</v>
       </c>
       <c r="S36" t="n">
-        <v>6637</v>
+        <v>6639</v>
       </c>
       <c r="T36" t="n">
-        <v>4.6084</v>
+        <v>4.6097</v>
       </c>
       <c r="U36" t="n">
-        <v>3.72</v>
+        <v>4.07</v>
       </c>
       <c r="V36" t="n">
-        <v>2.4981</v>
+        <v>2.4965</v>
       </c>
       <c r="W36" t="n">
-        <v>2.183</v>
+        <v>2.1816</v>
       </c>
       <c r="X36" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3764,76 +3764,76 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>37.603</v>
+        <v>37.604</v>
       </c>
       <c r="B37" t="n">
         <v>74.4616</v>
       </c>
       <c r="C37" t="n">
-        <v>169.90233</v>
+        <v>169.90234</v>
       </c>
       <c r="D37" t="n">
         <v>38</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4617</v>
+        <v>-1.4638</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.4619</v>
+        <v>-1.4639</v>
       </c>
       <c r="G37" t="n">
-        <v>24.015736</v>
+        <v>24.016195</v>
       </c>
       <c r="H37" t="n">
-        <v>24.015212</v>
+        <v>24.015685</v>
       </c>
       <c r="I37" t="n">
-        <v>29.7927</v>
+        <v>29.7974</v>
       </c>
       <c r="J37" t="n">
-        <v>29.7923</v>
+        <v>29.7968</v>
       </c>
       <c r="K37" t="n">
-        <v>345.763</v>
+        <v>345.31</v>
       </c>
       <c r="L37" t="n">
-        <v>340.714</v>
+        <v>340.316</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1743</v>
+        <v>0.1787</v>
       </c>
       <c r="N37" t="n">
         <v>4.6264</v>
       </c>
       <c r="O37" t="n">
-        <v>0.1156</v>
+        <v>0.1155</v>
       </c>
       <c r="P37" t="n">
-        <v>0.1156</v>
+        <v>0.1155</v>
       </c>
       <c r="Q37" t="n">
         <v>0.0538</v>
       </c>
       <c r="R37" t="n">
-        <v>0.0319</v>
+        <v>0.0321</v>
       </c>
       <c r="S37" t="n">
-        <v>6692</v>
+        <v>6694</v>
       </c>
       <c r="T37" t="n">
-        <v>4.6463</v>
+        <v>4.6476</v>
       </c>
       <c r="U37" t="n">
-        <v>9.51</v>
+        <v>9.64</v>
       </c>
       <c r="V37" t="n">
-        <v>2.4492</v>
+        <v>2.4466</v>
       </c>
       <c r="W37" t="n">
-        <v>2.148</v>
+        <v>2.1461</v>
       </c>
       <c r="X37" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>38.592</v>
+        <v>38.591</v>
       </c>
       <c r="B38" t="n">
         <v>74.4616</v>
@@ -3868,64 +3868,64 @@
         <v>39</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.4477</v>
+        <v>-1.447</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.4471</v>
+        <v>-1.4464</v>
       </c>
       <c r="G38" t="n">
-        <v>24.128776</v>
+        <v>24.132058</v>
       </c>
       <c r="H38" t="n">
-        <v>24.128701</v>
+        <v>24.131945</v>
       </c>
       <c r="I38" t="n">
-        <v>29.9319</v>
+        <v>29.9364</v>
       </c>
       <c r="J38" t="n">
-        <v>29.9312</v>
+        <v>29.9356</v>
       </c>
       <c r="K38" t="n">
-        <v>330.29</v>
+        <v>329.808</v>
       </c>
       <c r="L38" t="n">
-        <v>327.737</v>
+        <v>327.318</v>
       </c>
       <c r="M38" t="n">
-        <v>0.2778</v>
+        <v>0.2772</v>
       </c>
       <c r="N38" t="n">
-        <v>4.6266</v>
+        <v>4.6265</v>
       </c>
       <c r="O38" t="n">
-        <v>0.116</v>
+        <v>0.1159</v>
       </c>
       <c r="P38" t="n">
-        <v>0.116</v>
+        <v>0.1159</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.0536</v>
+        <v>0.0537</v>
       </c>
       <c r="R38" t="n">
         <v>0.0361</v>
       </c>
       <c r="S38" t="n">
-        <v>6751</v>
+        <v>6753</v>
       </c>
       <c r="T38" t="n">
-        <v>4.6875</v>
+        <v>4.6888</v>
       </c>
       <c r="U38" t="n">
-        <v>10.74</v>
+        <v>11.08</v>
       </c>
       <c r="V38" t="n">
-        <v>2.3642</v>
+        <v>2.3616</v>
       </c>
       <c r="W38" t="n">
-        <v>2.0882</v>
+        <v>2.0863</v>
       </c>
       <c r="X38" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -3960,64 +3960,64 @@
         <v>40</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4388</v>
+        <v>-1.4385</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4385</v>
+        <v>-1.4383</v>
       </c>
       <c r="G39" t="n">
-        <v>24.307172</v>
+        <v>24.311673</v>
       </c>
       <c r="H39" t="n">
-        <v>24.306236</v>
+        <v>24.310694</v>
       </c>
       <c r="I39" t="n">
-        <v>30.1651</v>
+        <v>30.1713</v>
       </c>
       <c r="J39" t="n">
-        <v>30.1635</v>
+        <v>30.1697</v>
       </c>
       <c r="K39" t="n">
-        <v>314.951</v>
+        <v>314.517</v>
       </c>
       <c r="L39" t="n">
-        <v>313.809</v>
+        <v>313.408</v>
       </c>
       <c r="M39" t="n">
-        <v>0.7079</v>
+        <v>0.7228</v>
       </c>
       <c r="N39" t="n">
-        <v>4.6154</v>
+        <v>4.6143</v>
       </c>
       <c r="O39" t="n">
-        <v>0.1195</v>
+        <v>0.1196</v>
       </c>
       <c r="P39" t="n">
-        <v>0.1195</v>
+        <v>0.1196</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.0633</v>
+        <v>0.0642</v>
       </c>
       <c r="R39" t="n">
-        <v>0.0533</v>
+        <v>0.0539</v>
       </c>
       <c r="S39" t="n">
-        <v>6805</v>
+        <v>6806</v>
       </c>
       <c r="T39" t="n">
-        <v>4.7249</v>
+        <v>4.726</v>
       </c>
       <c r="U39" t="n">
-        <v>6.71</v>
+        <v>6.58</v>
       </c>
       <c r="V39" t="n">
-        <v>2.2808</v>
+        <v>2.2785</v>
       </c>
       <c r="W39" t="n">
-        <v>2.0244</v>
+        <v>2.0226</v>
       </c>
       <c r="X39" t="n">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -4040,7 +4040,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>40.571</v>
+        <v>40.57</v>
       </c>
       <c r="B40" t="n">
         <v>74.4616</v>
@@ -4052,64 +4052,64 @@
         <v>41</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4173</v>
+        <v>-1.4166</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4169</v>
+        <v>-1.4163</v>
       </c>
       <c r="G40" t="n">
-        <v>24.560063</v>
+        <v>24.567038</v>
       </c>
       <c r="H40" t="n">
-        <v>24.560047</v>
+        <v>24.567212</v>
       </c>
       <c r="I40" t="n">
-        <v>30.4869</v>
+        <v>30.4953</v>
       </c>
       <c r="J40" t="n">
-        <v>30.4865</v>
+        <v>30.4951</v>
       </c>
       <c r="K40" t="n">
-        <v>300.092</v>
+        <v>299.764</v>
       </c>
       <c r="L40" t="n">
-        <v>298.969</v>
+        <v>298.556</v>
       </c>
       <c r="M40" t="n">
-        <v>0.9508</v>
+        <v>0.9584</v>
       </c>
       <c r="N40" t="n">
-        <v>4.5781</v>
+        <v>4.5775</v>
       </c>
       <c r="O40" t="n">
-        <v>0.1209</v>
+        <v>0.121</v>
       </c>
       <c r="P40" t="n">
-        <v>0.1209</v>
+        <v>0.121</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.0958</v>
+        <v>0.0963</v>
       </c>
       <c r="R40" t="n">
-        <v>0.063</v>
+        <v>0.0633</v>
       </c>
       <c r="S40" t="n">
-        <v>6857</v>
+        <v>6858</v>
       </c>
       <c r="T40" t="n">
-        <v>4.761</v>
+        <v>4.7618</v>
       </c>
       <c r="U40" t="n">
-        <v>8.87</v>
+        <v>8.74</v>
       </c>
       <c r="V40" t="n">
-        <v>2.2017</v>
+        <v>2.2</v>
       </c>
       <c r="W40" t="n">
-        <v>1.9576</v>
+        <v>1.9558</v>
       </c>
       <c r="X40" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -4132,7 +4132,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>41.56</v>
+        <v>41.561</v>
       </c>
       <c r="B41" t="n">
         <v>74.4616</v>
@@ -4144,64 +4144,64 @@
         <v>42</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.3811</v>
+        <v>-1.3795</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.3808</v>
+        <v>-1.3791</v>
       </c>
       <c r="G41" t="n">
-        <v>24.945364</v>
+        <v>24.960738</v>
       </c>
       <c r="H41" t="n">
-        <v>24.945578</v>
+        <v>24.961117</v>
       </c>
       <c r="I41" t="n">
-        <v>30.974</v>
+        <v>30.9918</v>
       </c>
       <c r="J41" t="n">
-        <v>30.974</v>
+        <v>30.992</v>
       </c>
       <c r="K41" t="n">
-        <v>281.117</v>
+        <v>280.503</v>
       </c>
       <c r="L41" t="n">
-        <v>148</v>
+        <v>137.089</v>
       </c>
       <c r="M41" t="n">
-        <v>1.1611</v>
+        <v>1.1958</v>
       </c>
       <c r="N41" t="n">
-        <v>4.5476</v>
+        <v>4.5457</v>
       </c>
       <c r="O41" t="n">
-        <v>0.1255</v>
+        <v>0.1253</v>
       </c>
       <c r="P41" t="n">
-        <v>0.1255</v>
+        <v>0.1253</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.1225</v>
+        <v>0.1242</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0714</v>
+        <v>0.0728</v>
       </c>
       <c r="S41" t="n">
-        <v>6906</v>
+        <v>6908</v>
       </c>
       <c r="T41" t="n">
-        <v>4.7954</v>
+        <v>4.7966</v>
       </c>
       <c r="U41" t="n">
-        <v>6</v>
+        <v>5.71</v>
       </c>
       <c r="V41" t="n">
-        <v>2.1013</v>
+        <v>2.0981</v>
       </c>
       <c r="W41" t="n">
-        <v>1.2339</v>
+        <v>1.1815</v>
       </c>
       <c r="X41" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>42.55</v>
+        <v>42.549</v>
       </c>
       <c r="B42" t="n">
         <v>74.46162</v>
@@ -4236,34 +4236,34 @@
         <v>43</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.3473</v>
+        <v>-1.3463</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.3469</v>
+        <v>-1.3459</v>
       </c>
       <c r="G42" t="n">
-        <v>25.414874</v>
+        <v>25.431738</v>
       </c>
       <c r="H42" t="n">
-        <v>25.415473</v>
+        <v>25.433006</v>
       </c>
       <c r="I42" t="n">
-        <v>31.5785</v>
+        <v>31.5983</v>
       </c>
       <c r="J42" t="n">
-        <v>31.5789</v>
+        <v>31.5996</v>
       </c>
       <c r="K42" t="n">
-        <v>257.525</v>
+        <v>256.892</v>
       </c>
       <c r="L42" t="n">
-        <v>244.207</v>
+        <v>246.62</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6584</v>
+        <v>0.6363</v>
       </c>
       <c r="N42" t="n">
-        <v>4.5326</v>
+        <v>4.5308</v>
       </c>
       <c r="O42" t="n">
         <v>0.1292</v>
@@ -4272,28 +4272,28 @@
         <v>0.1292</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.1357</v>
+        <v>0.1374</v>
       </c>
       <c r="R42" t="n">
-        <v>0.0513</v>
+        <v>0.0504</v>
       </c>
       <c r="S42" t="n">
-        <v>6964</v>
+        <v>6966</v>
       </c>
       <c r="T42" t="n">
-        <v>4.8355</v>
+        <v>4.8367</v>
       </c>
       <c r="U42" t="n">
-        <v>14.13</v>
+        <v>14.53</v>
       </c>
       <c r="V42" t="n">
-        <v>1.9747</v>
+        <v>1.9713</v>
       </c>
       <c r="W42" t="n">
-        <v>1.7066</v>
+        <v>1.7185</v>
       </c>
       <c r="X42" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -4316,7 +4316,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>43.539</v>
+        <v>43.54</v>
       </c>
       <c r="B43" t="n">
         <v>74.46162</v>
@@ -4328,64 +4328,64 @@
         <v>44</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.3131</v>
+        <v>-1.312</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.3126</v>
+        <v>-1.3115</v>
       </c>
       <c r="G43" t="n">
-        <v>25.859337</v>
+        <v>25.877548</v>
       </c>
       <c r="H43" t="n">
-        <v>25.861555</v>
+        <v>25.87978</v>
       </c>
       <c r="I43" t="n">
-        <v>32.1484</v>
+        <v>32.1695</v>
       </c>
       <c r="J43" t="n">
-        <v>32.1509</v>
+        <v>32.172</v>
       </c>
       <c r="K43" t="n">
-        <v>236.565</v>
+        <v>235.663</v>
       </c>
       <c r="L43" t="n">
-        <v>240.042</v>
+        <v>238.868</v>
       </c>
       <c r="M43" t="n">
-        <v>0.5191</v>
+        <v>0.5196</v>
       </c>
       <c r="N43" t="n">
-        <v>4.5554</v>
+        <v>4.557</v>
       </c>
       <c r="O43" t="n">
-        <v>0.1283</v>
+        <v>0.1285</v>
       </c>
       <c r="P43" t="n">
-        <v>0.1283</v>
+        <v>0.1285</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.1157</v>
+        <v>0.1143</v>
       </c>
       <c r="R43" t="n">
         <v>0.0458</v>
       </c>
       <c r="S43" t="n">
-        <v>7017</v>
+        <v>7018</v>
       </c>
       <c r="T43" t="n">
-        <v>4.872</v>
+        <v>4.8733</v>
       </c>
       <c r="U43" t="n">
-        <v>13.81</v>
+        <v>13.76</v>
       </c>
       <c r="V43" t="n">
-        <v>1.8614</v>
+        <v>1.8564</v>
       </c>
       <c r="W43" t="n">
-        <v>1.6925</v>
+        <v>1.687</v>
       </c>
       <c r="X43" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>44.529</v>
+        <v>44.53</v>
       </c>
       <c r="B44" t="n">
         <v>74.46162</v>
@@ -4426,58 +4426,58 @@
         <v>-1.278</v>
       </c>
       <c r="G44" t="n">
-        <v>26.320273</v>
+        <v>26.317119</v>
       </c>
       <c r="H44" t="n">
-        <v>26.322668</v>
+        <v>26.319091</v>
       </c>
       <c r="I44" t="n">
-        <v>32.7404</v>
+        <v>32.7335</v>
       </c>
       <c r="J44" t="n">
-        <v>32.7432</v>
+        <v>32.7357</v>
       </c>
       <c r="K44" t="n">
-        <v>209.098</v>
+        <v>207.423</v>
       </c>
       <c r="L44" t="n">
-        <v>210.534</v>
+        <v>203.272</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4397</v>
+        <v>0.4303</v>
       </c>
       <c r="N44" t="n">
-        <v>4.5689</v>
+        <v>4.5663</v>
       </c>
       <c r="O44" t="n">
-        <v>0.1306</v>
+        <v>0.1302</v>
       </c>
       <c r="P44" t="n">
-        <v>0.1306</v>
+        <v>0.1302</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.1038</v>
+        <v>0.1061</v>
       </c>
       <c r="R44" t="n">
-        <v>0.0426</v>
+        <v>0.0422</v>
       </c>
       <c r="S44" t="n">
-        <v>7081</v>
+        <v>7089</v>
       </c>
       <c r="T44" t="n">
-        <v>4.9164</v>
+        <v>4.9222</v>
       </c>
       <c r="U44" t="n">
-        <v>12.7</v>
+        <v>12.64</v>
       </c>
       <c r="V44" t="n">
-        <v>1.7093</v>
+        <v>1.6993</v>
       </c>
       <c r="W44" t="n">
-        <v>1.554</v>
+        <v>1.5181</v>
       </c>
       <c r="X44" t="n">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -4500,76 +4500,76 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>45.518</v>
+        <v>45.52</v>
       </c>
       <c r="B45" t="n">
-        <v>74.46177</v>
+        <v>74.46176</v>
       </c>
       <c r="C45" t="n">
-        <v>169.90271</v>
+        <v>169.90274</v>
       </c>
       <c r="D45" t="n">
         <v>46</v>
       </c>
       <c r="E45" t="n">
-        <v>-1.2476</v>
+        <v>-1.2384</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.2467</v>
+        <v>-1.2377</v>
       </c>
       <c r="G45" t="n">
-        <v>26.677062</v>
+        <v>26.801935</v>
       </c>
       <c r="H45" t="n">
-        <v>26.68215</v>
+        <v>26.805915</v>
       </c>
       <c r="I45" t="n">
-        <v>33.1943</v>
+        <v>33.3547</v>
       </c>
       <c r="J45" t="n">
-        <v>33.2003</v>
+        <v>33.3595</v>
       </c>
       <c r="K45" t="n">
-        <v>166.48</v>
+        <v>160.61</v>
       </c>
       <c r="L45" t="n">
-        <v>136.779</v>
+        <v>136.371</v>
       </c>
       <c r="M45" t="n">
-        <v>0.4573</v>
+        <v>0.3741</v>
       </c>
       <c r="N45" t="n">
-        <v>4.5793</v>
+        <v>4.5635</v>
       </c>
       <c r="O45" t="n">
-        <v>0.1297</v>
+        <v>0.1309</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1297</v>
+        <v>0.1309</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.0948</v>
+        <v>0.1087</v>
       </c>
       <c r="R45" t="n">
-        <v>0.0433</v>
+        <v>0.04</v>
       </c>
       <c r="S45" t="n">
-        <v>8155</v>
+        <v>8099</v>
       </c>
       <c r="T45" t="n">
-        <v>5.6623</v>
+        <v>5.6238</v>
       </c>
       <c r="U45" t="n">
-        <v>11.44</v>
+        <v>11.36</v>
       </c>
       <c r="V45" t="n">
-        <v>1.4657</v>
+        <v>1.433</v>
       </c>
       <c r="W45" t="n">
-        <v>1.1946</v>
+        <v>1.1939</v>
       </c>
       <c r="X45" t="n">
-        <v>17</v>
+        <v>173</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
